--- a/clients/showroom-real/catalog.xlsx
+++ b/clients/showroom-real/catalog.xlsx
@@ -1,41 +1,263 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yeyian PC\Documents\VSCodeProjects\3dvista-assistant\clients\showroom-real\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A03C67-AD5D-4ECB-9E6D-4F0BF6EF40C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView minimized="1" xWindow="10560" yWindow="3300" windowWidth="26145" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="77">
+  <si>
+    <t>product_id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>colors</t>
+  </si>
+  <si>
+    <t>materials</t>
+  </si>
+  <si>
+    <t>keywords</t>
+  </si>
+  <si>
+    <t>synonyms</t>
+  </si>
+  <si>
+    <t>section</t>
+  </si>
+  <si>
+    <t>media_name</t>
+  </si>
+  <si>
+    <t>yaw</t>
+  </si>
+  <si>
+    <t>pitch</t>
+  </si>
+  <si>
+    <t>fov</t>
+  </si>
+  <si>
+    <t>hotspot_name</t>
+  </si>
+  <si>
+    <t>image_url</t>
+  </si>
+  <si>
+    <t>detail_url</t>
+  </si>
+  <si>
+    <t>alternatives_group</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>mesa-comedor-milano-01</t>
+  </si>
+  <si>
+    <t>Mesa de Comedor Milano</t>
+  </si>
+  <si>
+    <t>mesas</t>
+  </si>
+  <si>
+    <t>Mesa de comedor rectangular en roble macizo, 200×90 cm, acabado natural que resalta la veta de la madera. Pieza central pensada para reunir a toda la familia.</t>
+  </si>
+  <si>
+    <t>roble natural</t>
+  </si>
+  <si>
+    <t>roble macizo</t>
+  </si>
+  <si>
+    <t>mesa,comedor,madera,rectangular,roble</t>
+  </si>
+  <si>
+    <t>mesa de comedor,mesa grande,mesa para comer</t>
+  </si>
+  <si>
+    <t>Sala 1 — Entrada</t>
+  </si>
+  <si>
+    <t>sala-1-entrada</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/mesa-comedor-milano-01/480/320</t>
+  </si>
+  <si>
+    <t>mesas-showroom-real</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>sofa-cama-milano-01</t>
+  </si>
+  <si>
+    <t>Sofá Cama Milano</t>
+  </si>
+  <si>
+    <t>sofás</t>
+  </si>
+  <si>
+    <t>Sofá cama de diseño italiano con estructura de madera maciza y tapizado en tela de alta resistencia. Se abre en segundos y se transforma en una amplia cama individual, ideal para espacios que combinan funcionalidad y estilo. Disponible en distintos acabados.</t>
+  </si>
+  <si>
+    <t>gris</t>
+  </si>
+  <si>
+    <t>madera maciza,tela</t>
+  </si>
+  <si>
+    <t>sofá,sofá cama,convertible,italiano</t>
+  </si>
+  <si>
+    <t>sillón cama,sofá convertible,divano letto</t>
+  </si>
+  <si>
+    <t>Sala 3 — Living</t>
+  </si>
+  <si>
+    <t>sala-3-living</t>
+  </si>
+  <si>
+    <t>assets/showroom-real/sofa-cama-milano-01.jpg</t>
+  </si>
+  <si>
+    <t>asientos-showroom-real</t>
+  </si>
+  <si>
+    <t>vitrina-vidrio-01</t>
+  </si>
+  <si>
+    <t>Vitrina Suspendida con Puertas de Vidrio</t>
+  </si>
+  <si>
+    <t>almacenamiento</t>
+  </si>
+  <si>
+    <t>Vitrina suspendida con puertas correderas de vidrio templado esmerilado. Estructura en fresno natural con iluminación LED integrada — perfecta para exhibir vajilla o piezas decorativas.</t>
+  </si>
+  <si>
+    <t>fresno natural</t>
+  </si>
+  <si>
+    <t>fresno,vidrio templado</t>
+  </si>
+  <si>
+    <t>vitrina,almacenamiento,vidrio,suspendida,LED</t>
+  </si>
+  <si>
+    <t>mueble vitrina,estantería con vidrio,alacena</t>
+  </si>
+  <si>
+    <t>Sala 2 — Vitrinas</t>
+  </si>
+  <si>
+    <t>sala-2-vitrinas</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/vitrina-vidrio-01/480/320</t>
+  </si>
+  <si>
+    <t>vitrinas-showroom-real</t>
+  </si>
+  <si>
+    <t>sillon-lounge-01</t>
+  </si>
+  <si>
+    <t>Sillón Giratorio Lounge</t>
+  </si>
+  <si>
+    <t>sillas</t>
+  </si>
+  <si>
+    <t>Sillón lounge giratorio tapizado en ecopiel blanca de flor entera. Base de cuatro radios en acero pintado negro mate — comodidad y diseño para espacios de descanso.</t>
+  </si>
+  <si>
+    <t>blanco</t>
+  </si>
+  <si>
+    <t>ecopiel,acero</t>
+  </si>
+  <si>
+    <t>sillón,lounge,giratorio,relax</t>
+  </si>
+  <si>
+    <t>poltrona,sillón reclinable,silla giratoria</t>
+  </si>
+  <si>
+    <t>Sala 4 — Lounge</t>
+  </si>
+  <si>
+    <t>sala-4-lounge</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/sillon-lounge-01/480/320</t>
+  </si>
+  <si>
+    <t>mesas-duo-01</t>
+  </si>
+  <si>
+    <t>Set de Mesas de Centro Duo</t>
+  </si>
+  <si>
+    <t>Set de dos mesas auxiliares apilables con tapa de vidrio ahumado y base de metal bronceado. Versátiles: se usan juntas o separadas según el espacio.</t>
+  </si>
+  <si>
+    <t>bronce,vidrio ahumado</t>
+  </si>
+  <si>
+    <t>vidrio,metal</t>
+  </si>
+  <si>
+    <t>mesa,mesa auxiliar,set,centro,vidrio</t>
+  </si>
+  <si>
+    <t>mesas de centro,mesas nido,mesitas</t>
+  </si>
+  <si>
+    <t>Sala 5 — Mesas</t>
+  </si>
+  <si>
+    <t>sala-5-mesas</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/mesas-duo-01/480/320</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -72,6 +294,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,95 +626,108 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.75" customWidth="1"/>
+    <col min="2" max="2" width="21.75" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="35.5" customWidth="1"/>
+    <col min="6" max="6" width="21.25" customWidth="1"/>
+    <col min="7" max="7" width="27.5" customWidth="1"/>
+    <col min="10" max="10" width="15.375" customWidth="1"/>
+    <col min="11" max="11" width="16.125" customWidth="1"/>
+    <col min="12" max="12" width="11.75" customWidth="1"/>
+    <col min="15" max="15" width="17.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>product_id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>category</v>
-      </c>
-      <c r="D1" t="str">
-        <v>description</v>
-      </c>
-      <c r="E1" t="str">
-        <v>colors</v>
-      </c>
-      <c r="F1" t="str">
-        <v>materials</v>
-      </c>
-      <c r="G1" t="str">
-        <v>keywords</v>
-      </c>
-      <c r="H1" t="str">
-        <v>synonyms</v>
-      </c>
-      <c r="I1" t="str">
-        <v>section</v>
-      </c>
-      <c r="J1" t="str">
-        <v>media_name</v>
-      </c>
-      <c r="K1" t="str">
-        <v>yaw</v>
-      </c>
-      <c r="L1" t="str">
-        <v>pitch</v>
-      </c>
-      <c r="M1" t="str">
-        <v>fov</v>
-      </c>
-      <c r="N1" t="str">
-        <v>hotspot_name</v>
-      </c>
-      <c r="O1" t="str">
-        <v>image_url</v>
-      </c>
-      <c r="P1" t="str">
-        <v>detail_url</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>alternatives_group</v>
-      </c>
-      <c r="R1" t="str">
-        <v>active</v>
+    <row r="1" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>mesa-comedor-milano-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Mesa de Comedor Milano</v>
-      </c>
-      <c r="C2" t="str">
-        <v>mesas</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Mesa de comedor rectangular en roble macizo, 200×90 cm, acabado natural que resalta la veta de la madera. Pieza central pensada para reunir a toda la familia.</v>
-      </c>
-      <c r="E2" t="str">
-        <v>roble natural</v>
-      </c>
-      <c r="F2" t="str">
-        <v>roble macizo</v>
-      </c>
-      <c r="G2" t="str">
-        <v>mesa,comedor,madera,rectangular,roble</v>
-      </c>
-      <c r="H2" t="str">
-        <v>mesa de comedor,mesa grande,mesa para comer</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Sala 1 — Entrada</v>
-      </c>
-      <c r="J2" t="str">
-        <v>sala-1-entrada</v>
+    <row r="2" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
       </c>
       <c r="K2">
         <v>122.568</v>
@@ -495,52 +738,52 @@
       <c r="M2">
         <v>65</v>
       </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v>https://picsum.photos/seed/mesa-comedor-milano-01/480/320</v>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v>mesas-showroom-real</v>
-      </c>
-      <c r="R2" t="str">
-        <v>TRUE</v>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>sofa-cama-milano-01</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Sofá Cama Milano</v>
-      </c>
-      <c r="C3" t="str">
-        <v>sofás</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Sofá cama de diseño italiano con estructura de madera maciza y tapizado en tela de alta resistencia. Se abre en segundos y se transforma en una amplia cama individual, ideal para espacios que combinan funcionalidad y estilo. Disponible en distintos acabados.</v>
-      </c>
-      <c r="E3" t="str">
-        <v>gris</v>
-      </c>
-      <c r="F3" t="str">
-        <v>madera maciza,tela</v>
-      </c>
-      <c r="G3" t="str">
-        <v>sofá,sofá cama,convertible,italiano</v>
-      </c>
-      <c r="H3" t="str">
-        <v>sillón cama,sofá convertible,divano letto</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Sala 3 — Living</v>
-      </c>
-      <c r="J3" t="str">
-        <v>sala-3-living</v>
+    <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" t="s">
+        <v>41</v>
       </c>
       <c r="K3">
         <v>110.631</v>
@@ -551,164 +794,164 @@
       <c r="M3">
         <v>65</v>
       </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v>assets/showroom-real/sofa-cama-milano-01.jpg</v>
-      </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-      <c r="Q3" t="str">
-        <v>asientos-showroom-real</v>
-      </c>
-      <c r="R3" t="str">
-        <v>TRUE</v>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R3" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>vitrina-vidrio-01</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Vitrina Suspendida con Puertas de Vidrio</v>
-      </c>
-      <c r="C4" t="str">
-        <v>almacenamiento</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Vitrina suspendida con puertas correderas de vidrio templado esmerilado. Estructura en fresno natural con iluminación LED integrada — perfecta para exhibir vajilla o piezas decorativas.</v>
-      </c>
-      <c r="E4" t="str">
-        <v>fresno natural</v>
-      </c>
-      <c r="F4" t="str">
-        <v>fresno,vidrio templado</v>
-      </c>
-      <c r="G4" t="str">
-        <v>vitrina,almacenamiento,vidrio,suspendida,LED</v>
-      </c>
-      <c r="H4" t="str">
-        <v>mueble vitrina,estantería con vidrio,alacena</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Sala 2 — Vitrinas</v>
-      </c>
-      <c r="J4" t="str">
-        <v>sala-2-vitrinas</v>
+    <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" t="s">
+        <v>53</v>
       </c>
       <c r="K4">
-        <v>155.263</v>
+        <v>155.26300000000001</v>
       </c>
       <c r="L4">
-        <v>3.612</v>
+        <v>3.6120000000000001</v>
       </c>
       <c r="M4">
         <v>65</v>
       </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v>https://picsum.photos/seed/vitrina-vidrio-01/480/320</v>
-      </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-      <c r="Q4" t="str">
-        <v>vitrinas-showroom-real</v>
-      </c>
-      <c r="R4" t="str">
-        <v>TRUE</v>
+      <c r="N4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" t="s">
+        <v>54</v>
+      </c>
+      <c r="P4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R4" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>sillon-lounge-01</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Sillón Giratorio Lounge</v>
-      </c>
-      <c r="C5" t="str">
-        <v>sillas</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Sillón lounge giratorio tapizado en ecopiel blanca de flor entera. Base de cuatro radios en acero pintado negro mate — comodidad y diseño para espacios de descanso.</v>
-      </c>
-      <c r="E5" t="str">
-        <v>blanco</v>
-      </c>
-      <c r="F5" t="str">
-        <v>ecopiel,acero</v>
-      </c>
-      <c r="G5" t="str">
-        <v>sillón,lounge,giratorio,relax</v>
-      </c>
-      <c r="H5" t="str">
-        <v>poltrona,sillón reclinable,silla giratoria</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Sala 4 — Lounge</v>
-      </c>
-      <c r="J5" t="str">
-        <v>sala-4-lounge</v>
+    <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" t="s">
+        <v>65</v>
       </c>
       <c r="K5">
         <v>173.91</v>
       </c>
       <c r="L5">
-        <v>-10.485</v>
+        <v>-10.484999999999999</v>
       </c>
       <c r="M5">
         <v>65</v>
       </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v>https://picsum.photos/seed/sillon-lounge-01/480/320</v>
-      </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-      <c r="Q5" t="str">
-        <v>asientos-showroom-real</v>
-      </c>
-      <c r="R5" t="str">
-        <v>TRUE</v>
+      <c r="N5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>43</v>
+      </c>
+      <c r="R5" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>mesas-duo-01</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Set de Mesas de Centro Duo</v>
-      </c>
-      <c r="C6" t="str">
-        <v>mesas</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Set de dos mesas auxiliares apilables con tapa de vidrio ahumado y base de metal bronceado. Versátiles: se usan juntas o separadas según el espacio.</v>
-      </c>
-      <c r="E6" t="str">
-        <v>bronce,vidrio ahumado</v>
-      </c>
-      <c r="F6" t="str">
-        <v>vidrio,metal</v>
-      </c>
-      <c r="G6" t="str">
-        <v>mesa,mesa auxiliar,set,centro,vidrio</v>
-      </c>
-      <c r="H6" t="str">
-        <v>mesas de centro,mesas nido,mesitas</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Sala 5 — Mesas</v>
-      </c>
-      <c r="J6" t="str">
-        <v>sala-5-mesas</v>
+    <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J6" t="s">
+        <v>75</v>
       </c>
       <c r="K6">
         <v>-174.251</v>
@@ -719,25 +962,26 @@
       <c r="M6">
         <v>65</v>
       </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v>https://picsum.photos/seed/mesas-duo-01/480/320</v>
-      </c>
-      <c r="P6" t="str">
-        <v/>
-      </c>
-      <c r="Q6" t="str">
-        <v>mesas-showroom-real</v>
-      </c>
-      <c r="R6" t="str">
-        <v>TRUE</v>
+      <c r="N6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" t="s">
+        <v>76</v>
+      </c>
+      <c r="P6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R6" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R6"/>
+    <ignoredError sqref="A1:R6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>